--- a/data_src/xlsx表/活动表.xlsx
+++ b/data_src/xlsx表/活动表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,6 +675,324 @@
         <is>
           <t>受舆论限制 0/1</t>
         </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>机场1</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>101</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O4" t="n">
+        <v>10</v>
+      </c>
+      <c r="P4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>机场2</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>102</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>10</v>
+      </c>
+      <c r="P5" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>机场3</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>103</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3</v>
+      </c>
+      <c r="N6" t="n">
+        <v>8</v>
+      </c>
+      <c r="O6" t="n">
+        <v>15</v>
+      </c>
+      <c r="P6" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>拼盘1</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>30</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>201</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>4</v>
+      </c>
+      <c r="N7" t="n">
+        <v>10</v>
+      </c>
+      <c r="O7" t="n">
+        <v>18</v>
+      </c>
+      <c r="P7" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>拼盘2</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>50</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>202</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O8" t="n">
+        <v>18</v>
+      </c>
+      <c r="P8" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>拼盘3</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>80</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>203</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N9" t="n">
+        <v>15</v>
+      </c>
+      <c r="O9" t="n">
+        <v>25</v>
+      </c>
+      <c r="P9" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data_src/xlsx表/活动表.xlsx
+++ b/data_src/xlsx表/活动表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -690,7 +690,7 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -704,7 +704,6 @@
       <c r="H4" t="n">
         <v>101</v>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
         <v>1</v>
       </c>
@@ -743,7 +742,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>20</v>
@@ -757,7 +756,6 @@
       <c r="H5" t="n">
         <v>102</v>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
         <v>1</v>
       </c>
@@ -796,7 +794,7 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -810,7 +808,6 @@
       <c r="H6" t="n">
         <v>103</v>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
         <v>1</v>
       </c>
@@ -863,7 +860,6 @@
       <c r="H7" t="n">
         <v>201</v>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
         <v>1</v>
       </c>
@@ -916,7 +912,6 @@
       <c r="H8" t="n">
         <v>202</v>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
         <v>1</v>
       </c>
@@ -969,7 +964,6 @@
       <c r="H9" t="n">
         <v>203</v>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
         <v>1</v>
       </c>
@@ -993,6 +987,60 @@
       </c>
       <c r="Q9" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>教程签售</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>301</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N10" t="n">
+        <v>10</v>
+      </c>
+      <c r="O10" t="n">
+        <v>18</v>
+      </c>
+      <c r="P10" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
